--- a/output/topology_excel/11451.xlsx
+++ b/output/topology_excel/11451.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -689,17 +689,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>339</v>
+        <v>581</v>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>367</v>
+        <v>339</v>
       </c>
       <c r="F13" t="n">
         <v>18</v>
@@ -726,11 +726,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
         <v>2</v>
       </c>
-      <c r="B14" t="n">
-        <v>3</v>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -740,7 +740,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>418</v>
+        <v>288</v>
       </c>
       <c r="F14" t="n">
         <v>18</v>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>132</v>
+        <v>270</v>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
@@ -795,7 +795,7 @@
         <v>2</v>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -817,7 +817,7 @@
         <v>2</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>270</v>
+        <v>132</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -839,7 +839,7 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>150</v>
+        <v>81</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         <v>2</v>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,19 +894,19 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>352</v>
+        <v>198</v>
       </c>
       <c r="F21" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" t="n">
         <v>4</v>
       </c>
-      <c r="B22" t="n">
-        <v>6</v>
-      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>430</v>
+        <v>352</v>
       </c>
       <c r="F22" t="n">
-        <v>18</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" t="n">
         <v>5</v>
-      </c>
-      <c r="B24" t="n">
-        <v>10</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" t="n">
         <v>8</v>
@@ -982,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="F25" t="n">
         <v>18</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B26" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="F26" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
@@ -1015,7 +1015,7 @@
         <v>6</v>
       </c>
       <c r="B27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,18 +1026,18 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="F27" t="n">
-        <v>107</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1056,11 +1056,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" t="n">
         <v>7</v>
       </c>
-      <c r="B29" t="n">
-        <v>10</v>
-      </c>
       <c r="C29" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1070,10 +1070,10 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="F29" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -1081,7 +1081,7 @@
         <v>7</v>
       </c>
       <c r="B30" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="F30" t="n">
         <v>15</v>
@@ -1103,7 +1103,7 @@
         <v>7</v>
       </c>
       <c r="B31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,19 +1114,19 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" t="n">
         <v>8</v>
       </c>
-      <c r="B32" t="n">
-        <v>9</v>
-      </c>
       <c r="C32" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>189</v>
+        <v>78</v>
       </c>
       <c r="F32" t="n">
         <v>15</v>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B33" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,15 +1158,15 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>150</v>
+        <v>62</v>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B34" t="n">
         <v>11</v>
@@ -1180,37 +1180,37 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F34" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" t="n">
+        <v>15</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>155</v>
+      </c>
+      <c r="F35" t="n">
         <v>10</v>
-      </c>
-      <c r="B35" t="n">
-        <v>12</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="n">
-        <v>62</v>
-      </c>
-      <c r="F35" t="n">
-        <v>43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B36" t="n">
         <v>12</v>
@@ -1224,18 +1224,18 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="F36" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>9</v>
+      </c>
+      <c r="B37" t="n">
         <v>11</v>
-      </c>
-      <c r="B37" t="n">
-        <v>13</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1249,7 +1249,139 @@
         <v>92</v>
       </c>
       <c r="F37" t="n">
-        <v>18</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>10</v>
+      </c>
+      <c r="B38" t="n">
+        <v>12</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>367</v>
+      </c>
+      <c r="F38" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>11</v>
+      </c>
+      <c r="B39" t="n">
+        <v>13</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>158</v>
+      </c>
+      <c r="F39" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>12</v>
+      </c>
+      <c r="B40" t="n">
+        <v>13</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>326</v>
+      </c>
+      <c r="F40" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>13</v>
+      </c>
+      <c r="B41" t="n">
+        <v>14</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>203</v>
+      </c>
+      <c r="F41" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>272</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>9</v>
+      </c>
+      <c r="B43" t="n">
+        <v>13</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>97</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/11451.xlsx
+++ b/output/topology_excel/11451.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
         <v>270</v>
       </c>
       <c r="F16" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -919,7 +919,7 @@
         <v>352</v>
       </c>
       <c r="F22" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -963,7 +963,7 @@
         <v>352</v>
       </c>
       <c r="F24" t="n">
-        <v>71</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
